--- a/evaluation/evaluation_results_1.xlsx
+++ b/evaluation/evaluation_results_1.xlsx
@@ -865,7 +865,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -876,20 +876,13 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -929,7 +922,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -938,9 +931,6 @@
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -1251,18 +1241,18 @@
   <dimension ref="A1:E31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="5" width="21.290714285714284" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="5" width="21.290714285714284" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="5" width="21.290714285714284" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="5" width="21.290714285714284" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="5" width="21.290714285714284" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="4" width="21.290714285714284" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="4" width="21.290714285714284" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="4" width="21.290714285714284" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="4" width="21.290714285714284" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="4" width="21.290714285714284" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
@@ -1275,513 +1265,513 @@
         <v>4</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="428.25" customFormat="1" s="1">
-      <c r="A2" s="4" t="s">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="474.75" customFormat="1" s="1">
+      <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="375.75" customFormat="1" s="1">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="890.25" customFormat="1" s="1">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="414.75" customFormat="1" s="1">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="3" t="s">
         <v>24</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="784.5" customFormat="1" s="1">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="3" t="s">
         <v>29</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="348.75" customFormat="1" s="1">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="3" t="s">
         <v>34</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="692.25" customFormat="1" s="1">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="3" t="s">
         <v>39</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="348.75" customFormat="1" s="1">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="3" t="s">
         <v>44</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="784.5" customFormat="1" s="1">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="3" t="s">
         <v>49</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="362.25" customFormat="1" s="1">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="3" t="s">
         <v>54</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="758.25" customFormat="1" s="1">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="3" t="s">
         <v>59</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="507.75" customFormat="1" s="1">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="3" t="s">
         <v>64</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="336" customFormat="1" s="1">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="3" t="s">
         <v>69</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="388.5" customFormat="1" s="1">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="3" t="s">
         <v>74</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="652.5" customFormat="1" s="1">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="3" t="s">
         <v>79</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="480.75" customFormat="1" s="1">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="E17" s="3" t="s">
         <v>84</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="652.5" customFormat="1" s="1">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="E18" s="3" t="s">
         <v>89</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="916.5" customFormat="1" s="1">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="E19" s="3" t="s">
         <v>94</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="890.25" customFormat="1" s="1">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="E20" s="3" t="s">
         <v>99</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="626.25" customFormat="1" s="1">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="E21" s="4" t="s">
+      <c r="E21" s="3" t="s">
         <v>104</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="692.25" customFormat="1" s="1">
-      <c r="A22" s="4" t="s">
+      <c r="A22" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="E22" s="4" t="s">
+      <c r="E22" s="3" t="s">
         <v>109</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="600" customFormat="1" s="1">
-      <c r="A23" s="4" t="s">
+      <c r="A23" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C23" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="E23" s="4" t="s">
+      <c r="E23" s="3" t="s">
         <v>114</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="837.75" customFormat="1" s="1">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C24" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="E24" s="3" t="s">
         <v>119</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="402" customFormat="1" s="1">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C25" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D25" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="E25" s="4" t="s">
+      <c r="E25" s="3" t="s">
         <v>124</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="480.75" customFormat="1" s="1">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="C26" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="D26" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="E26" s="4" t="s">
+      <c r="E26" s="3" t="s">
         <v>129</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A27" s="4" t="s">
+      <c r="A27" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="C27" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="D27" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="E27" s="4" t="s">
+      <c r="E27" s="3" t="s">
         <v>134</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A28" s="4" t="s">
+      <c r="A28" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="C28" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="D28" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="E28" s="4" t="s">
+      <c r="E28" s="3" t="s">
         <v>139</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A29" s="4" t="s">
+      <c r="A29" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B29" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="C29" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="D29" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="E29" s="4" t="s">
+      <c r="E29" s="3" t="s">
         <v>144</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A30" s="4" t="s">
+      <c r="A30" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B30" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="C30" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="D30" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E30" s="4" t="s">
+      <c r="E30" s="3" t="s">
         <v>149</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A31" s="4" t="s">
+      <c r="A31" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="B31" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="C31" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="D31" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="E31" s="4" t="s">
+      <c r="E31" s="3" t="s">
         <v>154</v>
       </c>
     </row>
